--- a/dcf/FIGR.xlsx
+++ b/dcf/FIGR.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1131,25 +1131,25 @@
         <v>12</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>69.28262380533178</v>
+        <v>52.71281603657654</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>66.52033506093683</v>
+        <v>50.71206382389738</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>63.8974450249202</v>
+        <v>48.81160371799356</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>61.40616620685056</v>
+        <v>47.00585024072992</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>59.03918452205219</v>
+        <v>45.28955689067332</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>56.78962828726128</v>
+        <v>43.65779396499201</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>54.65103938845207</v>
+        <v>42.10592793415726</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>73.05459332572292</v>
+        <v>55.40381011052852</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>70.11018076561648</v>
+        <v>53.27312733871954</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>67.31479319623253</v>
+        <v>51.24960424475247</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>64.66009073212406</v>
+        <v>49.32726126148759</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>62.13824106980121</v>
+        <v>47.5004821804328</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>59.7418862171092</v>
+        <v>45.76399035683738</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>57.46411155502939</v>
+        <v>44.11282658191565</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>76.82656284611407</v>
+        <v>58.09480418448049</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>73.70002647029617</v>
+        <v>55.83419085354168</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>70.73214136754488</v>
+        <v>53.68760477151137</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>67.91401525739755</v>
+        <v>51.64867228224524</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>65.23729761755024</v>
+        <v>49.71140747019228</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>62.69414414695713</v>
+        <v>47.87018674868274</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>60.27718372160673</v>
+        <v>46.11972522967404</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>80.59853236650521</v>
+        <v>60.78579825843248</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>77.28987217497584</v>
+        <v>58.39525436836383</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>74.1494895388572</v>
+        <v>56.12560529827027</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>71.16793978267106</v>
+        <v>53.97008330300291</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>68.33635416529926</v>
+        <v>51.92233275995175</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>65.64640207680506</v>
+        <v>49.97638314052811</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>63.09025588818405</v>
+        <v>48.12662387743244</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>84.37050188689635</v>
+        <v>63.47679233238445</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>80.8797178796555</v>
+        <v>60.95631788318598</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>77.56683771016954</v>
+        <v>58.56360582502919</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>74.42186430794456</v>
+        <v>56.29149432376058</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>71.43541071304827</v>
+        <v>54.13325804971122</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>68.59866000665299</v>
+        <v>52.08257953237347</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>65.90332805476137</v>
+        <v>50.13352252519081</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>17</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>88.14247140728749</v>
+        <v>66.16778640633643</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>84.46956358433515</v>
+        <v>63.51738139800813</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>80.98418588148188</v>
+        <v>61.00160635178808</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>77.67578883321805</v>
+        <v>58.61290534451824</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>74.53446726079729</v>
+        <v>56.3441833394707</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>71.55091793650092</v>
+        <v>54.18877592421883</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>68.7164002213387</v>
+        <v>52.14042117294921</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>91.91444092767861</v>
+        <v>68.85878048028842</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>88.05940928901482</v>
+        <v>66.07844491283028</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>84.40153405279422</v>
+        <v>63.43960687854698</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>80.92971335849155</v>
+        <v>60.9343163652759</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>77.63352380854631</v>
+        <v>58.55510862923018</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>74.50317586634884</v>
+        <v>56.2949723160642</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>71.52947238791603</v>
+        <v>54.14731982070761</v>
       </c>
     </row>
     <row r="13">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1.043509662895727</v>
+        <v>1.048962412442408</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>71.16793978267106</v>
+        <v>53.97008330300291</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>93.78879526576901</v>
+        <v>69.12094980086943</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>53.79147065927275</v>
+        <v>42.05383539393422</v>
       </c>
     </row>
     <row r="59">
